--- a/Mongodb/mongodb.xlsx
+++ b/Mongodb/mongodb.xlsx
@@ -1117,7 +1117,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1131,18 +1131,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1851,7 +1840,7 @@
       <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="3"/>
@@ -1860,10 +1849,10 @@
       <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="3"/>
@@ -1875,7 +1864,7 @@
       <c r="B19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D19" s="3"/>
@@ -1887,7 +1876,7 @@
       <c r="B20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D20" s="3"/>
@@ -1899,7 +1888,7 @@
       <c r="B21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D21" s="3"/>
@@ -1911,7 +1900,7 @@
       <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="3"/>
@@ -1923,7 +1912,7 @@
       <c r="B23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="3"/>
@@ -1981,31 +1970,31 @@
       </c>
     </row>
     <row r="29" ht="139.5" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="30" ht="42.75" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
     </row>
     <row r="31" ht="85.5" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2013,10 +2002,10 @@
       <c r="A32" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2024,10 +2013,10 @@
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="3" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2035,10 +2024,10 @@
       <c r="A34" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2046,28 +2035,28 @@
       <c r="A35" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
     </row>
     <row r="37" ht="285">
       <c r="A37" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="3" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2075,10 +2064,10 @@
       <c r="A38" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="3" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2086,116 +2075,116 @@
       <c r="A39" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="40" ht="256.5">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="41" ht="242.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="42" ht="228">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="43" ht="356.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
     </row>
     <row r="45" ht="85.5">
       <c r="A45" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="3" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="46" ht="356.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="47" ht="114">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="48" ht="114">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="49" ht="199.5">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="3" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2206,7 +2195,7 @@
       <c r="B50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2217,7 +2206,7 @@
       <c r="B51" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="3" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2225,21 +2214,21 @@
       <c r="A52" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="3" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="53" ht="313.5">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="3" t="s">
         <v>146</v>
       </c>
     </row>
